--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-12-2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,15 +511,10 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Building Materials Direct</t>
+          <t>Insulation Bee</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Insulation Bee</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DIY Building supplies</t>
         </is>
@@ -608,15 +603,10 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£23.87</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
-        <is>
-          <t>£23.87</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
         <is>
           <t>£10.15</t>
         </is>
@@ -705,15 +695,10 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£27.67</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
-        <is>
-          <t>£27.67</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
         <is>
           <t>£11.87</t>
         </is>
@@ -802,15 +787,10 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£29.74</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
-        <is>
-          <t>£29.74</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
         <is>
           <t>£15.15</t>
         </is>
@@ -899,15 +879,10 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£32.42</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
-        <is>
-          <t>£32.42</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
         <is>
           <t>£15.71</t>
         </is>
@@ -996,15 +971,10 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£39.12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
-        <is>
-          <t>£39.12</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
         <is>
           <t>£19.22</t>
         </is>
@@ -1093,15 +1063,10 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£46.64</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
-        <is>
-          <t>£46.64</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
         <is>
           <t>£22.14</t>
         </is>
@@ -1165,7 +1130,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£20.30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1190,15 +1155,10 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£46.55</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
-        <is>
-          <t>£46.55</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
         <is>
           <t>£21.34</t>
         </is>
@@ -1287,15 +1247,10 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£51.7</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
-        <is>
-          <t>£51.7</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
         <is>
           <t>£23.98</t>
         </is>
@@ -1384,15 +1339,10 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£57.31</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
-        <is>
-          <t>£57.31</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
         <is>
           <t>£27.08</t>
         </is>
@@ -1481,15 +1431,10 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£49.55</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
-        <is>
-          <t>£49.55</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
         <is>
           <t>£26.67</t>
         </is>
@@ -1578,15 +1523,10 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
         <is>
           <t>£32.74</t>
         </is>
@@ -1675,15 +1615,10 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£74.18</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
-        <is>
-          <t>£74.18</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
         <is>
           <t>£33.13</t>
         </is>
@@ -1772,15 +1707,10 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£81.55</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
-        <is>
-          <t>£81.55</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
         <is>
           <t>£40.04</t>
         </is>
@@ -1829,7 +1759,36 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£37.59</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 299.424
+  (Session info: chrome=143.0.7499.147)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff7bde488e5
+	0x7ff7bde48940
+	0x7ff7bdc2165d
+	0x7ff7bdc0e847
+	0x7ff7bdc0e5bd
+	0x7ff7bdc0c20a
+	0x7ff7bdc0cbcf
+	0x7ff7bdc1bb8a
+	0x7ff7bdc3223f
+	0x7ff7bdc3940a
+	0x7ff7bdc0d375
+	0x7ff7bdc31df2
+	0x7ff7bdccb080
+	0x7ff7bdc6ac29
+	0x7ff7bdc6ba93
+	0x7ff7be160640
+	0x7ff7be15af80
+	0x7ff7be1796e6
+	0x7ff7bde65de4
+	0x7ff7bde6ed8c
+	0x7ff7bde52004
+	0x7ff7bde521b5
+	0x7ff7bde37ee2
+	0x7ffa9660e8d7
+	0x7ffa97e0c53c
+</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1869,15 +1828,10 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£86.21</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
-        <is>
-          <t>£86.21</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
         <is>
           <t>N/L</t>
         </is>
@@ -1966,15 +1920,10 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£89.87</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
-        <is>
-          <t>£89.87</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
         <is>
           <t>£40.45</t>
         </is>
@@ -2063,15 +2012,10 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
         <is>
           <t>N/L</t>
         </is>
@@ -2160,15 +2104,10 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
         <is>
           <t>£852.50 Pre Sale Price-£889.80</t>
         </is>
@@ -2257,15 +2196,10 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£51.2</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
-        <is>
-          <t>£51.2</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
         <is>
           <t>£29.28 Pre Sale Price-£30.00</t>
         </is>
@@ -2354,15 +2288,10 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>£59.2</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
-        <is>
-          <t>£59.2</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
         <is>
           <t>£35.60 Pre Sale Price-£35.83</t>
         </is>
@@ -2451,15 +2380,10 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£79.58</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
-        <is>
-          <t>£79.58</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
         <is>
           <t>£38.56 Pre Sale Price-£40.83</t>
         </is>
@@ -2548,15 +2472,10 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>£70.18</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
-        <is>
-          <t>£70.18</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
         <is>
           <t>£43.59 Pre Sale Price-£45.83</t>
         </is>
@@ -2645,15 +2564,10 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
         <is>
           <t>£46.36</t>
         </is>
@@ -2742,15 +2656,10 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
         <is>
           <t>£45.63</t>
         </is>
@@ -2839,15 +2748,10 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>N/L</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
         <is>
           <t>N/L</t>
         </is>
@@ -2936,15 +2840,10 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
         <is>
           <t>£43.97</t>
         </is>
@@ -3038,11 +2937,6 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
           <t>£1257.76</t>
         </is>
       </c>
@@ -3135,11 +3029,6 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
           <t>£1366.4</t>
         </is>
       </c>
@@ -3231,11 +3120,6 @@
         </is>
       </c>
       <c r="R29" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
         <is>
           <t>£1358.08</t>
         </is>
